--- a/device-model-indicators/太敏_指标库_20260225.xlsx
+++ b/device-model-indicators/太敏_指标库_20260225.xlsx
@@ -163,7 +163,7 @@
     <col min="10" max="10" width="6.6640625" customWidth="true"/>
     <col min="11" max="11" width="6.6640625" customWidth="true"/>
     <col min="12" max="12" width="4.5546875" customWidth="true"/>
-    <col min="13" max="13" width="5.21875" customWidth="true"/>
+    <col min="13" max="13" width="4.5546875" customWidth="true"/>
     <col min="14" max="14" width="5.21875" customWidth="true"/>
     <col min="15" max="15" width="5.21875" customWidth="true"/>
     <col min="16" max="16" width="5.5546875" customWidth="true"/>
@@ -735,116 +735,48 @@
       <c r="B11" s="0">
         <v>65</v>
       </c>
-      <c r="C11" s="0">
-        <v>0</v>
-      </c>
+      <c r="C11" s="0"/>
       <c r="D11" s="0">
         <v>90</v>
       </c>
-      <c r="E11" s="0">
-        <v>45</v>
-      </c>
-      <c r="F11" s="0">
-        <v>2.3999999999999999</v>
-      </c>
-      <c r="G11" s="0">
-        <v>10</v>
-      </c>
-      <c r="H11" s="0">
-        <v>5000</v>
-      </c>
-      <c r="I11" s="0">
-        <v>5000</v>
-      </c>
-      <c r="J11" s="0">
-        <v>5000</v>
-      </c>
-      <c r="K11" s="0">
-        <v>5000</v>
-      </c>
-      <c r="L11" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="M11" s="0">
-        <v>-0.050000000000000003</v>
-      </c>
-      <c r="N11" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="O11" s="0">
-        <v>-0.050000000000000003</v>
-      </c>
-      <c r="P11" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="Q11" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="R11" s="0">
-        <v>5500</v>
-      </c>
-      <c r="S11" s="0">
-        <v>0.5</v>
-      </c>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="0">
-        <v>80</v>
-      </c>
-      <c r="C12" s="0">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0">
-        <v>90</v>
-      </c>
-      <c r="E12" s="0">
-        <v>45</v>
-      </c>
-      <c r="F12" s="0">
-        <v>4.7999999999999998</v>
-      </c>
-      <c r="G12" s="0">
-        <v>10</v>
-      </c>
-      <c r="H12" s="0">
-        <v>5000</v>
-      </c>
-      <c r="I12" s="0">
-        <v>5000</v>
-      </c>
-      <c r="J12" s="0">
-        <v>5000</v>
-      </c>
-      <c r="K12" s="0">
-        <v>5000</v>
-      </c>
-      <c r="L12" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="M12" s="0">
-        <v>-0.050000000000000003</v>
-      </c>
-      <c r="N12" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="O12" s="0">
-        <v>-0.050000000000000003</v>
-      </c>
-      <c r="P12" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="Q12" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="R12" s="0">
-        <v>5500</v>
-      </c>
-      <c r="S12" s="0">
-        <v>0.5</v>
-      </c>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
+      <c r="S12" s="0"/>
     </row>
   </sheetData>
 </worksheet>

--- a/device-model-indicators/太敏_指标库_20260225.xlsx
+++ b/device-model-indicators/太敏_指标库_20260225.xlsx
@@ -102,7 +102,7 @@
     <t>LX630SNS90</t>
   </si>
   <si>
-    <t>YYMQ9SNS90</t>
+    <t>YYMQ9SNS</t>
   </si>
 </sst>
 </file>
@@ -296,7 +296,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="D3" s="0">
         <v>44</v>
@@ -441,7 +441,7 @@
         <v>-0.20000000000000001</v>
       </c>
       <c r="N5" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="O5" s="0">
         <v>-0.10000000000000001</v>
@@ -450,7 +450,7 @@
         <v>0.5</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="R5" s="0">
         <v>5500</v>
@@ -733,7 +733,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="0">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0">
